--- a/labs/day6/roi_kpi_template.xlsx
+++ b/labs/day6/roi_kpi_template.xlsx
@@ -590,7 +590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성형 AI 기반 무역 금융 리스크 최적화 과정 · 6일차 Step 5(5교시) · 03 Part2 §6.8</t>
+          <t>생성형 AI 기반 무역 금융 리스크 최적화 과정 · 6일차 실습 B Step 5(14:12–14:50)</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>노랑 = 입력 · 회색 = 계산(고치지 않는다) · 파랑 = 출처가 있는 기준값</t>
+          <t>노랑 = 입력 · 회색 = 계산(고치지 않는다) · 파랑 = 기준값</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>10_KPI(DSO · BPDSO · ADD · CEI · 30일 초과 연체 비중 · 대손율 · DSO 감소율 · 미수금 발생률) · 20_ROI(팀 3안, 편집) · 21_Walkthrough(워크스루 고정 사본) · 30_ToolCost(도구비 S0–S3 · 운영비 계산기) · 40_MyKPI(나만의 KPI 3개) · 50_TimeLog(1주 타임로그) · 60_Sensitivity(신뢰도 × DSO 단축 민감도 — C 트랙) · 70_Benchmark(목표 설정 기준)</t>
+          <t>10_KPI(DSO · BPDSO · ADD · CEI · 30일 초과 연체 비중 · 대손율 · DSO 감소율 · 미수금 발생률) · 20_ROI(팀 3안, 편집) · 21_Walkthrough(워크스루 고정 사본) · 30_ToolCost(도구비 S0–S3 · 운영비 계산기) · 40_MyKPI(나만의 KPI 3개) · 50_TimeLog(1주 타임로그) · 60_Sensitivity(신뢰도 × DSO 단축 민감도 — 선택) · 70_Benchmark(목표 설정 기준)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>이 파일을 `d6_roi__T{조}-{번호}.xlsx`로 저장 → 40_MyKPI 3행 + (S 트랙) 자사 값으로 보수안 → 17:50 비공개 폼. 저장소에 올리지 않는다</t>
+          <t>이 파일을 `d6_roi__T{조}-{번호}.xlsx`로 저장 → 40_MyKPI 3행 + (선택) 자사 값으로 보수안 → 17:50 비공개 폼. 저장소에 올리지 않는다</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>재무 AI ROI 중앙값 10%(BCG)와 비교한 문장을 한 줄 쓴다. 기준안이 중앙값보다 훨씬 크면 인과 근거(파일럿 전후 비교)를 붙인다</t>
+          <t>재무 AI ROI 중앙값 10%(2025년 조사)와 비교한 문장을 한 줄 쓴다. 기준안이 중앙값보다 훨씬 크면 인과 근거(파일럿 전후 비교)를 붙인다</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>계획서의 '미수금 전수조사 시간 90% 단축'은 목표의 예일 뿐 근거가 아니다 — 기준선은 1주 타임로그로 잰다</t>
+          <t>'미수금 전수조사 시간 90% 단축' 같은 문장은 목표의 예일 뿐 근거가 아니다 — 기준선은 1주 타임로그로 잰다</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>CRF 예: 분기 신용매출 3,000 · 기말 1,400(정상 900) · 기초 1,300(천 달러) → DSO 42 · BPDSO 27 · ADD 15 · CEI 64.3% (10_KPI C열)</t>
+          <t>검산 예: 분기 신용매출 3,000 · 기말 1,400(정상 900) · 기초 1,300(천 달러) → DSO 42 · BPDSO 27 · ADD 15 · CEI 64.3% (10_KPI C열)</t>
         </is>
       </c>
     </row>
@@ -758,14 +758,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>10_KPI — 매출채권 KPI(CRF 정의) · DSO 감소율 · 미수금 발생률</t>
+          <t>10_KPI — 매출채권 KPI(표준 정의) · DSO 감소율 · 미수금 발생률</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>C열 = CRF 검산 예(천 달러) — 고치지 않는다 · D열 = 우리 값(노랑, 익명화한 자사 값이나 [교육용 가정]) · 회색 = 계산</t>
+          <t>C열 = 검산 예(천 달러) — 고치지 않는다 · D열 = 우리 값(노랑, 익명화한 자사 값이나 [교육용 가정]) · 회색 = 계산</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>검산 예(CRF)</t>
+          <t>검산 예</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>설명 · 출처</t>
+          <t>설명 · 근거</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>현금매출 제외 [R10]</t>
+          <t>현금매출 제외</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>IFRS 9 30일 추정선 · K-SURE 30일 면책선과 정렬 [R01]</t>
+          <t>회계 30일 추정선 · 보험 30일 면책선과 맞춘다</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>기말 총채권 × 일수 ÷ 기간 신용매출 [CRF · R01]</t>
+          <t>기말 총채권 × 일수 ÷ 기간 신용매출</t>
         </is>
       </c>
     </row>
@@ -1368,21 +1368,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>20_ROI — 팀 ROI 3안(보수 · 기준 · 낙관) · 03 Part2 §6.8 산식</t>
+          <t>20_ROI — 팀 ROI 3안(보수 · 기준 · 낙관)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>노랑 = 입력(지금은 워크스루 [교육용 가정] 값 — 우리 값으로 바꾼다) · 회색 = 계산(고치지 않는다) · 파랑 = 출처가 있는 기준값</t>
+          <t>노랑 = 입력(지금은 워크스루 [교육용 가정] 값 — 우리 값으로 바꾼다) · 회색 = 계산(고치지 않는다) · 파랑 = 기준값</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>보수안부터 보여 준다(측정 가능한 시간 절감만) · 숫자마다 출처나 [교육용 가정]을 붙인다 · 무형 효과(사기 차단 · 면책 회피)는 숫자에 넣지 않는다</t>
+          <t>보수안부터 보여 준다(측정 가능한 시간 절감만) · 숫자마다 근거나 [교육용 가정]을 붙인다 · 무형 효과(사기 차단 · 면책 회피)는 숫자에 넣지 않는다</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>설명 · 출처</t>
+          <t>설명 · 근거</t>
         </is>
       </c>
     </row>
@@ -1673,9 +1673,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G13" s="4">
-        <f> 연 대손상각액 ÷ 연 신용매출(10_KPI) · 참고 C27 중소 0.67%(G01)</f>
-        <v/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>연 대손상각액 ÷ 연 신용매출(10_KPI의 대손율) · 참고: 의료·정밀·광학 중소 0.67%(70_Benchmark)</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -1935,7 +1936,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>DSO_Cut × CreditSales_Y ÷ 365 [R10 추정 산식]</t>
+          <t>DSO_Cut × CreditSales_Y ÷ 365 (추정 산식)</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2266,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>BCG 재무 AI ROI 중앙값 10%(목표 20%) [R04]</t>
+          <t>재무 AI ROI 중앙값 10%(목표 20%, 2025년 조사)</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2278,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>BCG 재무 AI ROI 중앙값</t>
+          <t>재무 AI ROI 중앙값(2025년 조사)</t>
         </is>
       </c>
       <c r="C37" s="23" t="n">
@@ -2288,7 +2289,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>C = 중앙값 10% · D = 목표 20% — BCG(2025-06) [R04]. 기준안 ROI가 중앙값의 몇 배인지 한 줄로 비교한다</t>
+          <t>C = 중앙값 10% · D = 목표 20% (2025년 재무 임원 조사). 기준안 ROI가 중앙값의 몇 배인지 한 줄로 비교한다</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2323,7 @@
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>연 발생확률 × 평균 면책액 — 총편익에 넣으려면 근거(사례 · 확률)를 함께 적는다. K-SURE 공식 사례: U$1,000천 수출 중 U$650천 미회수, U$350천 면책 [R01]</t>
+          <t>연 발생확률 × 평균 면책액 — 총편익에 넣으려면 근거(사례 · 확률)를 함께 적는다. 예: 수출 U$1,000천 중 U$650천 미회수, U$350천 면책(보험 안내의 사례)</t>
         </is>
       </c>
       <c r="D41" s="25" t="n"/>
@@ -2360,14 +2361,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>21_Walkthrough — ROI 워크스루(고정) · 03 Part2 §6.8 산식</t>
+          <t>21_Walkthrough — ROI 워크스루(고정)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>고정 사본 — 03 Part2 §6.8 · 슬라이드와 같은 워크스루. 고치지 않는다(비교 기준 · 그림 IMG:d6-#20-a가 이 시트를 읽는다)</t>
+          <t>고정 사본 — 슬라이드와 같은 워크스루. 고치지 않는다(내 값과 견줄 때 쓰는 기준 값)</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2412,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>설명 · 출처</t>
+          <t>설명 · 근거</t>
         </is>
       </c>
     </row>
@@ -2665,9 +2666,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="G13" s="4">
-        <f> 연 대손상각액 ÷ 연 신용매출(10_KPI) · 참고 C27 중소 0.67%(G01)</f>
-        <v/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>연 대손상각액 ÷ 연 신용매출(10_KPI의 대손율) · 참고: 의료·정밀·광학 중소 0.67%(70_Benchmark)</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -2927,7 +2929,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>DSO_Cut × CreditSales_Y ÷ 365 [R10 추정 산식]</t>
+          <t>DSO_Cut × CreditSales_Y ÷ 365 (추정 산식)</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3259,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>BCG 재무 AI ROI 중앙값 10%(목표 20%) [R04]</t>
+          <t>재무 AI ROI 중앙값 10%(목표 20%, 2025년 조사)</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3271,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>BCG 재무 AI ROI 중앙값</t>
+          <t>재무 AI ROI 중앙값(2025년 조사)</t>
         </is>
       </c>
       <c r="C37" s="23" t="n">
@@ -3280,7 +3282,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>C = 중앙값 10% · D = 목표 20% — BCG(2025-06) [R04]. 기준안 ROI가 중앙값의 몇 배인지 한 줄로 비교한다</t>
+          <t>C = 중앙값 10% · D = 목표 20% (2025년 재무 임원 조사). 기준안 ROI가 중앙값의 몇 배인지 한 줄로 비교한다</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3320,7 @@
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>연 발생확률 × 평균 면책액 — 총편익에 넣으려면 근거(사례 · 확률)를 함께 적는다. K-SURE 공식 사례: U$1,000천 수출 중 U$650천 미회수, U$350천 면책 [R01]</t>
+          <t>연 발생확률 × 평균 면책액 — 총편익에 넣으려면 근거(사례 · 확률)를 함께 적는다. 예: 수출 U$1,000천 중 U$650천 미회수, U$350천 면책(보험 안내의 사례)</t>
         </is>
       </c>
       <c r="D41" s="25" t="n"/>
@@ -3363,7 +3365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>research G04 §2.5(교수자 산정, 2026-09-26 확인 — 벤더 공개값, 성과 보장 아님) · VAT 기준이 행마다 다르다</t>
+          <t>벤더 공개 가격으로 추정한 값(2026-09 확인, 성과 보장 아님) · VAT 기준이 행마다 다르다</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3608,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>계산기 값은 예시 [교육용 가정] — 과정의 LiteLLM 키는 10/22 만료라 자사 도입 때는 자사 계약 단가로 다시 잰다</t>
+          <t>계산기 값은 예시 [교육용 가정] — 자사 도입 때는 자사 계약 단가와 실제 사용 기록으로 다시 잰다</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>40_MyKPI — 나만의 KPI 3개(제안-KPI = P6-6 · 기획서 3장)</t>
+          <t>40_MyKPI — 나만의 KPI 3개(프롬프트 P6-6 · 기획서 3장)</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3759,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>데이터 출처</t>
+          <t>데이터 원천</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4331,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>60_Sensitivity — 기준안 ROI의 민감도: DSO 단축 일수 × DSO 효과 신뢰도(C 트랙)</t>
+          <t>60_Sensitivity — 기준안 ROI의 민감도: DSO 단축 일수 × DSO 효과 신뢰도(선택)</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4568,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>70_Benchmark — 목표 설정 기준(03 Part2 §6.8)</t>
+          <t>70_Benchmark — 목표 설정 기준</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4592,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>근거</t>
+          <t>읽는 법</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4604,12 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>약 58일 · 의료·정밀·광학(C27) 73일 · 기타기계(C29) 70일</t>
+          <t>약 58일 · 의료·정밀·광학 73일 · 기타기계 70일</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>한국은행 기업경영분석 [G01]</t>
+          <t>국내 통계 — 우리 업종 값을 본다</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4621,12 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>제조업 중소 0.31% · C27 중소 0.67%</t>
+          <t>제조업 중소 0.31% · 의료·정밀·광학 중소 0.67%</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>[G01]</t>
+          <t>국내 통계 — 대손율 기준선의 참고</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4638,12 @@
       </c>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>Hackett 중앙값 46일 · 상위 28일 · Billtrust 고객 39일(해외 대기업 중심)</t>
+          <t>조사 중앙값 46일 · 상위 28일 · 결제 SaaS 고객 평균 39일(해외 대기업 중심)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>[R04]</t>
+          <t>규모가 다르다 — 목표가 아니라 참고</t>
         </is>
       </c>
     </row>
@@ -4653,19 +4655,19 @@
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>Yaskawa America DSO −5.5일 · CEI 약 90%(매출 36억 달러 대기업 · 벤더 사례) · BCG 재무 AI 중앙값 ROI 10%(목표 20%)</t>
+          <t>일본계 제조사 미국 법인 DSO −5.5일 · CEI 약 90%(매출 36억 달러 대기업 · 벤더 사례) · 재무 AI 중앙값 ROI 10%(목표 20%, 2025년 조사)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[R04][G04]</t>
+          <t>벤더 사례 — 일반화하지 않는다</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>계획서 예시</t>
+          <t>목표 문장 예시</t>
         </is>
       </c>
       <c r="B10" s="36" t="inlineStr">
@@ -4675,7 +4677,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>교수계획서</t>
+          <t>기준선부터</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4694,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>[G02]</t>
+          <t>공공조달 업무</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4711,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[G04]</t>
+          <t>과장 없이 측정부터</t>
         </is>
       </c>
     </row>
